--- a/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,99; 37,84</t>
+          <t>21,46; 37,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,15; 37,87</t>
+          <t>24,1; 37,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 33,56</t>
+          <t>20,53; 33,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,36; 92,01</t>
+          <t>78,93; 91,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,79; 39,31</t>
+          <t>24,18; 38,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,19; 41,99</t>
+          <t>27,25; 42,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,68; 39,05</t>
+          <t>23,94; 38,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,3; 87,78</t>
+          <t>71,98; 87,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 35,59</t>
+          <t>25,04; 36,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,75; 38,01</t>
+          <t>27,45; 38,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 34,16</t>
+          <t>23,96; 34,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,2; 88,26</t>
+          <t>77,84; 88,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,77; 37,08</t>
+          <t>25,18; 36,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,97; 41,1</t>
+          <t>28,4; 40,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,25; 36,29</t>
+          <t>24,58; 35,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,1; 82,07</t>
+          <t>70,71; 82,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,43; 40,69</t>
+          <t>29,7; 40,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,79; 35,48</t>
+          <t>24,53; 35,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,27; 35,6</t>
+          <t>24,65; 34,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,23; 82,48</t>
+          <t>71,64; 82,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,17; 36,93</t>
+          <t>28,88; 37,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,95; 35,67</t>
+          <t>27,85; 36,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,41; 34,43</t>
+          <t>26,49; 34,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,38; 80,66</t>
+          <t>73,1; 80,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,81; 46,01</t>
+          <t>28,53; 46,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,34; 48,25</t>
+          <t>31,56; 48,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,56; 39,34</t>
+          <t>26,97; 39,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,59; 84,23</t>
+          <t>73,61; 84,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 48,27</t>
+          <t>32,77; 49,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,13; 47,15</t>
+          <t>31,36; 46,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,78; 43,25</t>
+          <t>30,39; 44,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68,98; 80,79</t>
+          <t>69,65; 81,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,57; 44,5</t>
+          <t>32,97; 45,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,54; 44,92</t>
+          <t>33,78; 45,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,51; 39,47</t>
+          <t>30,51; 40,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,26; 80,76</t>
+          <t>73,36; 81,04</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,1; 41,49</t>
+          <t>29,52; 42,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 44,26</t>
+          <t>30,26; 45,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,14; 54,06</t>
+          <t>39,41; 54,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,51; 83,33</t>
+          <t>69,65; 83,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,14; 47,45</t>
+          <t>35,24; 48,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,62; 47,01</t>
+          <t>33,69; 47,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 42,83</t>
+          <t>28,64; 43,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,28; 79,7</t>
+          <t>63,29; 79,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,85; 43,07</t>
+          <t>33,96; 43,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,66; 43,5</t>
+          <t>33,98; 44,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,21; 47,2</t>
+          <t>36,3; 46,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,04; 79,15</t>
+          <t>68,58; 79,23</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,33</t>
+          <t>29,7; 36,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,16</t>
+          <t>32,1; 39,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,69; 37,3</t>
+          <t>31,04; 37,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,65; 81,5</t>
+          <t>74,32; 81,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 40,4</t>
+          <t>33,88; 40,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,81; 38,71</t>
+          <t>32,03; 38,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,28; 36,87</t>
+          <t>30,35; 36,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,22; 78,63</t>
+          <t>71,37; 79,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,83; 37,65</t>
+          <t>32,76; 37,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,69; 37,54</t>
+          <t>32,85; 37,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,33; 36,24</t>
+          <t>31,23; 35,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,89; 79,25</t>
+          <t>74,12; 79,18</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22950</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31949</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27404</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49913</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27741</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38883</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31124</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>49696</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>50691</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>70832</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58528</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99609</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>16858; 29392</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25094; 39281</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21084; 34189</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>45395; 52847</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>21391; 34416</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30528; 47472</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23522; 38117</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>44226; 54059</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>41820; 60731</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>59342; 82581</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>48162; 68606</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>92594; 105108</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>57343</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46814</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>122079</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66007</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57272</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>141645</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>123350</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>112168</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>110255</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>263724</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>47146; 68203</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45250; 64669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38413; 55660</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112639; 130729</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>56055; 76758</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>47393; 67907</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>51916; 73499</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130787; 150571</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>108601; 139214</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>98205; 128202</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>97179; 126022</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>249892; 276603</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>32057</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39290</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47613</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138428</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42116</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39953</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49181</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>160666</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>74173</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79243</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>96795</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>299094</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>24676; 40601</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30926; 47919</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38921; 56943</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127991; 147033</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33842; 50638</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31928; 47765</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>40161; 58622</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>147997; 172647</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>62554; 86170</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>67489; 91360</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>84354; 111405</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>283435; 313117</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>53285</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42936</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57313</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>208326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61347</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53210</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>224441</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>114632</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>96145</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>103910</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>432767</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>44597; 64107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34960; 52089</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48118; 66836</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>191867; 228755</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>52194; 71094</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>44366; 63105</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>37233; 56267</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>193343; 243081</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>101584; 129588</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>84017; 109433</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>91527; 117992</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>398387; 460291</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>165636</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>169071</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>179144</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>518745</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>576450</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>362846</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>358388</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>369487</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1095195</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>149513; 182265</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>153090; 187837</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>163082; 198848</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>495054; 541281</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>179082; 213526</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>172586; 208284</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>173316; 207870</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>543841; 602518</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>338020; 386435</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>333641; 385221</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>342393; 393868</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1058540; 1130723</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,46; 37,41</t>
+          <t>21,56; 37,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,1; 37,73</t>
+          <t>22,85; 38,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,53; 33,29</t>
+          <t>20,46; 34,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,93; 91,89</t>
+          <t>79,3; 91,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,18; 38,9</t>
+          <t>24,07; 39,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,25; 42,37</t>
+          <t>26,77; 42,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,94; 38,79</t>
+          <t>24,63; 39,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,98; 87,98</t>
+          <t>71,91; 88,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,04; 36,36</t>
+          <t>24,5; 35,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,45; 38,2</t>
+          <t>27,85; 38,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,96; 34,14</t>
+          <t>24,1; 34,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,84; 88,36</t>
+          <t>77,98; 88,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 36,42</t>
+          <t>25,29; 35,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,4; 40,58</t>
+          <t>29,11; 41,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 35,62</t>
+          <t>24,47; 36,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,71; 82,07</t>
+          <t>70,99; 82,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,7; 40,67</t>
+          <t>29,65; 40,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,53; 35,14</t>
+          <t>24,23; 35,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,65; 34,9</t>
+          <t>25,22; 35,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,64; 82,48</t>
+          <t>72,1; 82,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,88; 37,03</t>
+          <t>28,72; 36,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,85; 36,36</t>
+          <t>27,54; 35,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,49; 34,35</t>
+          <t>26,51; 34,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,1; 80,91</t>
+          <t>73,45; 80,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,53; 46,95</t>
+          <t>29,12; 45,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,56; 48,91</t>
+          <t>31,98; 48,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 39,46</t>
+          <t>27,13; 40,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,61; 84,56</t>
+          <t>73,59; 84,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 49,04</t>
+          <t>33,65; 50,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,36; 46,92</t>
+          <t>31,55; 47,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,39; 44,35</t>
+          <t>30,88; 44,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,65; 81,25</t>
+          <t>70,43; 80,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,97; 45,41</t>
+          <t>33,67; 45,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,78; 45,73</t>
+          <t>34,37; 45,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,51; 40,29</t>
+          <t>30,29; 39,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,36; 81,04</t>
+          <t>73,65; 81,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 42,43</t>
+          <t>28,85; 42,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 45,09</t>
+          <t>29,27; 45,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,41; 54,74</t>
+          <t>38,82; 54,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,65; 83,05</t>
+          <t>69,09; 82,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,24; 48,01</t>
+          <t>35,56; 48,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,69; 47,91</t>
+          <t>33,75; 48,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,64; 43,28</t>
+          <t>28,76; 43,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,29; 79,57</t>
+          <t>63,41; 79,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,96; 43,32</t>
+          <t>33,9; 42,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 44,27</t>
+          <t>33,95; 43,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,3; 46,8</t>
+          <t>35,92; 46,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,58; 79,23</t>
+          <t>68,87; 79,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,7; 36,21</t>
+          <t>29,43; 36,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,38</t>
+          <t>32,1; 39,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 37,85</t>
+          <t>30,92; 37,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,32; 81,25</t>
+          <t>74,28; 81,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,88; 40,4</t>
+          <t>33,95; 40,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,03; 38,66</t>
+          <t>32,02; 38,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,35; 36,4</t>
+          <t>29,68; 36,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,37; 79,07</t>
+          <t>71,53; 78,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,76; 37,45</t>
+          <t>32,73; 37,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 37,92</t>
+          <t>32,81; 37,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,23; 35,92</t>
+          <t>31,59; 36,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,12; 79,18</t>
+          <t>73,79; 78,81</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16858; 29392</t>
+          <t>16940; 29645</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25094; 39281</t>
+          <t>23794; 40428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21084; 34189</t>
+          <t>21009; 35000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45395; 52847</t>
+          <t>45607; 52905</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21391; 34416</t>
+          <t>21298; 34684</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30528; 47472</t>
+          <t>29993; 47549</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23522; 38117</t>
+          <t>24202; 38882</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44226; 54059</t>
+          <t>44187; 54212</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41820; 60731</t>
+          <t>40913; 59921</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59342; 82581</t>
+          <t>60198; 82242</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48162; 68606</t>
+          <t>48443; 68655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92594; 105108</t>
+          <t>92762; 105294</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47146; 68203</t>
+          <t>47346; 67171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45250; 64669</t>
+          <t>46378; 65524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38413; 55660</t>
+          <t>38235; 56746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112639; 130729</t>
+          <t>113082; 130627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56055; 76758</t>
+          <t>55957; 77079</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47393; 67907</t>
+          <t>46812; 67663</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51916; 73499</t>
+          <t>53121; 74555</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>130787; 150571</t>
+          <t>131623; 150934</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108601; 139214</t>
+          <t>107986; 138494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98205; 128202</t>
+          <t>97080; 126561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97179; 126022</t>
+          <t>97247; 126131</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>249892; 276603</t>
+          <t>251076; 276670</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24676; 40601</t>
+          <t>25185; 39429</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30926; 47919</t>
+          <t>31334; 47239</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38921; 56943</t>
+          <t>39160; 58499</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127991; 147033</t>
+          <t>127973; 146531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33842; 50638</t>
+          <t>34750; 51651</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31928; 47765</t>
+          <t>32118; 48325</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40161; 58622</t>
+          <t>40818; 58913</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>147997; 172647</t>
+          <t>149654; 171808</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62554; 86170</t>
+          <t>63890; 85544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67489; 91360</t>
+          <t>68670; 91598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84354; 111405</t>
+          <t>83737; 109116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>283435; 313117</t>
+          <t>284567; 314253</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44597; 64107</t>
+          <t>43587; 64091</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34960; 52089</t>
+          <t>33814; 52337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48118; 66836</t>
+          <t>47396; 66681</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>191867; 228755</t>
+          <t>190325; 227500</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52194; 71094</t>
+          <t>52662; 72465</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44366; 63105</t>
+          <t>44450; 63239</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37233; 56267</t>
+          <t>37394; 55973</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>193343; 243081</t>
+          <t>193722; 243344</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101584; 129588</t>
+          <t>101429; 127773</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84017; 109433</t>
+          <t>83923; 108757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91527; 117992</t>
+          <t>90553; 117734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>398387; 460291</t>
+          <t>400082; 460614</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149513; 182265</t>
+          <t>148119; 182107</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153090; 187837</t>
+          <t>153097; 186219</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163082; 198848</t>
+          <t>162427; 199215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>495054; 541281</t>
+          <t>494793; 542431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>179082; 213526</t>
+          <t>179464; 214454</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>172586; 208284</t>
+          <t>172497; 208367</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>173316; 207870</t>
+          <t>169476; 207926</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>543841; 602518</t>
+          <t>545068; 601628</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>338020; 386435</t>
+          <t>337770; 388260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>333641; 385221</t>
+          <t>333254; 384731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>342393; 393868</t>
+          <t>346326; 396908</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1058540; 1130723</t>
+          <t>1053870; 1125460</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31,36%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>29,21%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30,68%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26,68%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,56; 37,74</t>
+          <t>22,79; 39,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 38,83</t>
+          <t>27,19; 41,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 34,08</t>
+          <t>24,68; 39,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,3; 91,99</t>
+          <t>73,48; 88,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 39,21</t>
+          <t>21,99; 37,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,77; 42,44</t>
+          <t>23,15; 37,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,63; 39,57</t>
+          <t>19,98; 33,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,91; 88,23</t>
+          <t>79,04; 92,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 35,88</t>
+          <t>24,6; 35,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,85; 38,05</t>
+          <t>27,75; 38,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,1; 34,16</t>
+          <t>24,06; 34,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,98; 88,52</t>
+          <t>79,11; 88,68</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>30,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>34,45%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>29,96%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,29; 35,87</t>
+          <t>29,43; 40,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,11; 41,12</t>
+          <t>23,79; 35,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,47; 36,31</t>
+          <t>25,27; 35,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,99; 82,0</t>
+          <t>73,42; 83,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,65; 40,84</t>
+          <t>25,77; 37,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,23; 35,02</t>
+          <t>27,97; 41,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 35,4</t>
+          <t>24,25; 36,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,1; 82,68</t>
+          <t>70,05; 81,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,72; 36,84</t>
+          <t>29,17; 36,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,54; 35,9</t>
+          <t>27,95; 35,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,51; 34,38</t>
+          <t>26,41; 34,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,45; 80,93</t>
+          <t>73,67; 81,0</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75,7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>37,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40,1%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>32,99%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79,61%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>40,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,12; 45,59</t>
+          <t>33,51; 48,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,98; 48,21</t>
+          <t>31,13; 47,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 40,54</t>
+          <t>29,78; 43,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,59; 84,27</t>
+          <t>69,5; 80,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,65; 50,02</t>
+          <t>28,81; 46,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 47,46</t>
+          <t>32,34; 48,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,88; 44,57</t>
+          <t>26,56; 39,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,43; 80,85</t>
+          <t>73,91; 84,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,67; 45,08</t>
+          <t>33,57; 44,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,37; 45,85</t>
+          <t>33,54; 44,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,29; 39,47</t>
+          <t>30,51; 39,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,65; 81,33</t>
+          <t>73,35; 80,79</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75,83%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>35,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37,17%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>46,94%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 42,42</t>
+          <t>35,14; 47,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 45,31</t>
+          <t>33,62; 47,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 54,61</t>
+          <t>29,2; 42,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,09; 82,59</t>
+          <t>68,02; 81,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,56; 48,93</t>
+          <t>29,1; 41,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,75; 48,02</t>
+          <t>29,54; 44,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,76; 43,06</t>
+          <t>39,14; 54,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,41; 79,66</t>
+          <t>70,6; 79,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,9; 42,71</t>
+          <t>33,85; 43,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 43,99</t>
+          <t>33,66; 43,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,92; 46,7</t>
+          <t>36,21; 47,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,87; 79,29</t>
+          <t>71,25; 79,11</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,43; 36,18</t>
+          <t>33,89; 40,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,04</t>
+          <t>31,81; 38,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,92; 37,92</t>
+          <t>30,28; 36,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,28; 81,43</t>
+          <t>73,12; 79,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,57</t>
+          <t>29,64; 36,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,02; 38,67</t>
+          <t>31,76; 39,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,41</t>
+          <t>30,69; 37,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,53; 78,96</t>
+          <t>74,71; 80,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,73; 37,63</t>
+          <t>32,83; 37,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,81; 37,88</t>
+          <t>32,69; 37,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,59; 36,2</t>
+          <t>31,33; 36,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,79; 78,81</t>
+          <t>74,89; 79,3</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27741</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38883</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31124</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41376</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22950</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>31949</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>27404</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49913</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>27741</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38883</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31124</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99609</t>
+          <t>86519</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16940; 29645</t>
+          <t>20162; 34772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23794; 40428</t>
+          <t>30469; 47051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21009; 35000</t>
+          <t>24257; 38369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45607; 52905</t>
+          <t>37135; 44632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21298; 34684</t>
+          <t>17271; 29725</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29993; 47549</t>
+          <t>24104; 39427</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24202; 38882</t>
+          <t>20516; 34471</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44187; 54212</t>
+          <t>41169; 48088</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40913; 59921</t>
+          <t>41082; 59439</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60198; 82242</t>
+          <t>59990; 82160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48443; 68655</t>
+          <t>48353; 68650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92762; 105294</t>
+          <t>81186; 91006</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>201</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66007</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63441</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>124240</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>57343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>54896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>46814</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>122079</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66007</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57272</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63441</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>141645</t>
+          <t>110151</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>263724</t>
+          <t>234390</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47346; 67171</t>
+          <t>55548; 76793</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46378; 65524</t>
+          <t>45976; 68563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38235; 56746</t>
+          <t>53209; 74975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113082; 130627</t>
+          <t>115649; 131333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55957; 77079</t>
+          <t>48260; 69430</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46812; 67663</t>
+          <t>44574; 65483</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53121; 74555</t>
+          <t>37896; 56703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>131623; 150934</t>
+          <t>101929; 118121</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107986; 138494</t>
+          <t>109658; 138855</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97080; 126561</t>
+          <t>98559; 125754</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97247; 126131</t>
+          <t>96884; 126310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>251076; 276670</t>
+          <t>223261; 245467</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39953</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49181</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151505</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>32057</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>39290</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>47613</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>138428</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42116</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39953</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49181</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>160666</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>299094</t>
+          <t>291520</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25185; 39429</t>
+          <t>34599; 49841</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31334; 47239</t>
+          <t>31695; 48007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39160; 58499</t>
+          <t>39357; 57170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127973; 146531</t>
+          <t>139087; 162075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34750; 51651</t>
+          <t>24915; 39785</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32118; 48325</t>
+          <t>31683; 47272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40818; 58913</t>
+          <t>38337; 56766</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>149654; 171808</t>
+          <t>129717; 147956</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63890; 85544</t>
+          <t>63691; 84432</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68670; 91598</t>
+          <t>67003; 89750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83737; 109116</t>
+          <t>84365; 109140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>284567; 314253</t>
+          <t>275532; 303470</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>251</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61347</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53210</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>221920</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>53285</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>42936</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>57313</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>208326</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>61347</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53210</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>46597</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>224441</t>
+          <t>192601</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>432767</t>
+          <t>414521</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43587; 64091</t>
+          <t>52033; 70268</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33814; 52337</t>
+          <t>44279; 61913</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47396; 66681</t>
+          <t>37966; 55684</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190325; 227500</t>
+          <t>199062; 238500</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52662; 72465</t>
+          <t>43967; 62680</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44450; 63239</t>
+          <t>34119; 51131</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37394; 55973</t>
+          <t>47788; 66009</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>193722; 243344</t>
+          <t>181133; 203773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101429; 127773</t>
+          <t>101257; 128846</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83923; 108757</t>
+          <t>83219; 107532</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90553; 117734</t>
+          <t>91288; 119005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>400082; 460614</t>
+          <t>391314; 434475</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>731</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>518745</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487909</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1095195</t>
+          <t>1026950</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>148119; 182107</t>
+          <t>179147; 213532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153097; 186219</t>
+          <t>171369; 208553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162427; 199215</t>
+          <t>172936; 210538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>494793; 542431</t>
+          <t>512446; 559254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>179464; 214454</t>
+          <t>149198; 182885</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>172497; 208367</t>
+          <t>151473; 186786</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>169476; 207926</t>
+          <t>161254; 195993</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>545068; 601628</t>
+          <t>470432; 505171</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>337770; 388260</t>
+          <t>338740; 388537</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>333254; 384731</t>
+          <t>332062; 381335</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>346326; 396908</t>
+          <t>343486; 397367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1053870; 1125460</t>
+          <t>996381; 1055093</t>
         </is>
       </c>
     </row>
